--- a/verificables revisión sistemática/S10_idioma_verificado_sobre_texto_completo.xlsx
+++ b/verificables revisión sistemática/S10_idioma_verificado_sobre_texto_completo.xlsx
@@ -677,7 +677,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-08-26</t>
+          <t>Generado el 2026-08-28</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S10_idioma_verificado_sobre_texto_completo.xlsx
+++ b/verificables revisión sistemática/S10_idioma_verificado_sobre_texto_completo.xlsx
@@ -677,7 +677,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-08-28</t>
+          <t>Generado el 2026-08-31</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S10_idioma_verificado_sobre_texto_completo.xlsx
+++ b/verificables revisión sistemática/S10_idioma_verificado_sobre_texto_completo.xlsx
@@ -677,7 +677,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-08-31</t>
+          <t>Generado el 2026-09-01</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S10_idioma_verificado_sobre_texto_completo.xlsx
+++ b/verificables revisión sistemática/S10_idioma_verificado_sobre_texto_completo.xlsx
@@ -677,7 +677,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-01</t>
+          <t>Generado el 2026-09-02</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S10_idioma_verificado_sobre_texto_completo.xlsx
+++ b/verificables revisión sistemática/S10_idioma_verificado_sobre_texto_completo.xlsx
@@ -677,7 +677,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-02</t>
+          <t>Generado el 2026-09-14</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S10_idioma_verificado_sobre_texto_completo.xlsx
+++ b/verificables revisión sistemática/S10_idioma_verificado_sobre_texto_completo.xlsx
@@ -677,7 +677,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-14</t>
+          <t>Generado el 2026-09-15</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S10_idioma_verificado_sobre_texto_completo.xlsx
+++ b/verificables revisión sistemática/S10_idioma_verificado_sobre_texto_completo.xlsx
@@ -677,7 +677,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-15</t>
+          <t>Generado el 2026-09-16</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S10_idioma_verificado_sobre_texto_completo.xlsx
+++ b/verificables revisión sistemática/S10_idioma_verificado_sobre_texto_completo.xlsx
@@ -677,7 +677,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-16</t>
+          <t>Generado el 2026-09-22</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S10_idioma_verificado_sobre_texto_completo.xlsx
+++ b/verificables revisión sistemática/S10_idioma_verificado_sobre_texto_completo.xlsx
@@ -677,7 +677,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-22</t>
+          <t>Generado el 2026-09-23</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S10_idioma_verificado_sobre_texto_completo.xlsx
+++ b/verificables revisión sistemática/S10_idioma_verificado_sobre_texto_completo.xlsx
@@ -677,7 +677,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-23</t>
+          <t>Generado el 2026-10-03</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S10_idioma_verificado_sobre_texto_completo.xlsx
+++ b/verificables revisión sistemática/S10_idioma_verificado_sobre_texto_completo.xlsx
@@ -677,7 +677,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-03</t>
+          <t>Generado el 2026-10-06</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S10_idioma_verificado_sobre_texto_completo.xlsx
+++ b/verificables revisión sistemática/S10_idioma_verificado_sobre_texto_completo.xlsx
@@ -677,7 +677,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-06</t>
+          <t>Generado el 2026-10-07</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S10_idioma_verificado_sobre_texto_completo.xlsx
+++ b/verificables revisión sistemática/S10_idioma_verificado_sobre_texto_completo.xlsx
@@ -677,7 +677,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-07</t>
+          <t>Generado el 2026-10-08</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S10_idioma_verificado_sobre_texto_completo.xlsx
+++ b/verificables revisión sistemática/S10_idioma_verificado_sobre_texto_completo.xlsx
@@ -677,7 +677,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-08</t>
+          <t>Generado el 2026-10-12</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S10_idioma_verificado_sobre_texto_completo.xlsx
+++ b/verificables revisión sistemática/S10_idioma_verificado_sobre_texto_completo.xlsx
@@ -667,7 +667,7 @@
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-14</t>
+          <t>Generado el 2026-10-15</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S10_idioma_verificado_sobre_texto_completo.xlsx
+++ b/verificables revisión sistemática/S10_idioma_verificado_sobre_texto_completo.xlsx
@@ -667,7 +667,7 @@
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-15</t>
+          <t>Generado el 2026-10-19</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S10_idioma_verificado_sobre_texto_completo.xlsx
+++ b/verificables revisión sistemática/S10_idioma_verificado_sobre_texto_completo.xlsx
@@ -667,7 +667,7 @@
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-19</t>
+          <t>Generado el 2026-10-20</t>
         </is>
       </c>
     </row>
